--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0015.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0015.xlsx
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan cất Broadblade vào eo khi thực hiện Basic Attack</t>
+          <t>Chụp ảnh Jiyan cất Đại kiếm vào eo khi thực hiện Basic Attack</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan cất Broadblade vào eo khi thực hiện Basic Attack</t>
+          <t>Chụp ảnh Jiyan cất Đại kiếm vào eo khi thực hiện Basic Attack</t>
         </is>
       </c>
     </row>
